--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>391056</v>
+        <v>140972</v>
       </c>
       <c r="B2" t="n">
-        <v>81235</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>633798.2077937282</v>
+        <v>633798</v>
       </c>
       <c r="R2" t="n">
-        <v>7235571.194362091</v>
+        <v>7235571</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -748,19 +743,9 @@
           <t>2005-10-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-10-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,49 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>520615</v>
+        <v>391056</v>
       </c>
       <c r="B3" t="n">
-        <v>89741</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633798.2077937282</v>
+        <v>633798</v>
       </c>
       <c r="R3" t="n">
-        <v>7235571.194362091</v>
+        <v>7235571</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -860,19 +840,9 @@
           <t>2005-10-28</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2005-10-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,49 +857,44 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>140972</v>
+        <v>520615</v>
       </c>
       <c r="B4" t="n">
-        <v>89337</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>112</v>
+        <v>1506</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>633798.2077937282</v>
+        <v>633798</v>
       </c>
       <c r="R4" t="n">
-        <v>7235571.194362091</v>
+        <v>7235571</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -972,19 +937,9 @@
           <t>2005-10-28</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2005-10-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1014,12 +969,7 @@
         <v>1881737</v>
       </c>
       <c r="B5" t="n">
-        <v>78502</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80336</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>633798.2077937282</v>
+        <v>633798</v>
       </c>
       <c r="R5" t="n">
-        <v>7235571.194362091</v>
+        <v>7235571</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1084,19 +1034,9 @@
           <t>2005-10-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2005-10-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,127 +1051,15 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sveaskog Västerbotten</t>
+          <t>Daniella Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Sveaskog Västerbotten</t>
+          <t>Via Daniella Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>1543951</v>
-      </c>
-      <c r="B6" t="n">
-        <v>89409</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Stormyran, Ly lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>633798.2077937282</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7235571.194362091</v>
-      </c>
-      <c r="S6" t="n">
-        <v>100</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Lycksele lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Sorsele</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2005-10-28</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2005-10-28</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Sveaskog Västerbotten</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Via Sveaskog Västerbotten</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39882-2025 artfynd.xlsx
+++ b/artfynd/A 39882-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/140972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/391056</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/520615</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,8 +1080,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1881737</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>